--- a/ABA_mining/outputs/eval/task3/staff/llama3.2/contrary_v3/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/staff/llama3.2/contrary_v3/EVAL_SUMMARY.xlsx
@@ -541,13 +541,13 @@
         <v>60</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3321428571428571</v>
+        <v>0.332143</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6078431372549019</v>
+        <v>0.607843</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4295612009237875</v>
+        <v>0.429561</v>
       </c>
       <c r="O2" t="n">
         <v>0.506</v>
@@ -600,13 +600,13 @@
         <v>60</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3321428571428571</v>
+        <v>0.332143</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6078431372549019</v>
+        <v>0.607843</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4295612009237875</v>
+        <v>0.429561</v>
       </c>
       <c r="O3" t="n">
         <v>0.506</v>
@@ -659,13 +659,13 @@
         <v>60</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3321428571428571</v>
+        <v>0.332143</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6078431372549019</v>
+        <v>0.607843</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4295612009237875</v>
+        <v>0.429561</v>
       </c>
       <c r="O4" t="n">
         <v>0.506</v>
@@ -784,13 +784,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.3321428571428571</v>
+        <v>0.332143</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6078431372549019</v>
+        <v>0.607843</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4295612009237875</v>
+        <v>0.429561</v>
       </c>
       <c r="I2" t="n">
         <v>0.506</v>
